--- a/survey_templates/043_structured_interview_survey--survey_templates.xlsx
+++ b/survey_templates/043_structured_interview_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Evaluation Scale 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Action Items</t>
+          <t>Follow Up Action Items</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Overall Rating 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Feedback Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Follow Up Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Action Items</t>
+          <t>Follow Up Action Items 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Overall Rating 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_or_disagree'}</t>
+          <t>neither_agree_or_disagree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree or Disagree'}</t>
+          <t>Neither Agree or Disagree</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_or_disagree'}</t>
+          <t>neither_agree_or_disagree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree or Disagree'}</t>
+          <t>Neither Agree or Disagree</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
